--- a/참고사항/TimingChart.xlsx
+++ b/참고사항/TimingChart.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -275,19 +275,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -953,192 +953,192 @@
       <c r="A30" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9" t="s">
+      <c r="B30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S30" s="10"/>
+      <c r="S30" s="13"/>
     </row>
     <row r="31" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="13">
-        <v>1</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13">
-        <v>0</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13">
-        <v>0</v>
-      </c>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13">
-        <v>0</v>
-      </c>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13" t="s">
+      <c r="B31" s="9">
+        <v>1</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9">
+        <v>0</v>
+      </c>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S31" s="13"/>
+      <c r="S31" s="9"/>
     </row>
     <row r="32" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13" t="s">
+      <c r="E32" s="9"/>
+      <c r="F32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13" t="s">
+      <c r="G32" s="9"/>
+      <c r="H32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13" t="s">
+      <c r="I32" s="9"/>
+      <c r="J32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13" t="s">
+      <c r="K32" s="9"/>
+      <c r="L32" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13" t="s">
+      <c r="M32" s="9"/>
+      <c r="N32" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13" t="s">
+      <c r="O32" s="9"/>
+      <c r="P32" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q32" s="13"/>
-      <c r="R32" s="13" t="s">
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S32" s="13"/>
+      <c r="S32" s="9"/>
     </row>
     <row r="33" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13" t="s">
+      <c r="C33" s="9"/>
+      <c r="D33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13" t="s">
+      <c r="E33" s="9"/>
+      <c r="F33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13" t="s">
+      <c r="G33" s="9"/>
+      <c r="H33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13" t="s">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13" t="s">
+      <c r="K33" s="9"/>
+      <c r="L33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13" t="s">
+      <c r="M33" s="9"/>
+      <c r="N33" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13" t="s">
+      <c r="O33" s="9"/>
+      <c r="P33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="13" t="s">
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S33" s="13"/>
+      <c r="S33" s="9"/>
     </row>
     <row r="34" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="13">
-        <v>0</v>
-      </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13">
-        <v>0</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13">
-        <v>1</v>
-      </c>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13">
-        <v>1</v>
-      </c>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13">
-        <v>1</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13">
-        <v>0</v>
-      </c>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="13" t="s">
+      <c r="B34" s="9">
+        <v>0</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9">
+        <v>1</v>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9">
+        <v>1</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9">
+        <v>1</v>
+      </c>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S34" s="13"/>
+      <c r="S34" s="9"/>
       <c r="T34" s="6" t="s">
         <v>17</v>
       </c>
@@ -1171,110 +1171,110 @@
       <c r="A52" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="9" t="s">
+      <c r="B52" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S52" s="10"/>
+      <c r="S52" s="13"/>
     </row>
     <row r="53" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="13">
-        <v>1</v>
-      </c>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13">
-        <v>0</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13">
-        <v>1</v>
-      </c>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13">
-        <v>0</v>
-      </c>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13">
-        <v>0</v>
-      </c>
-      <c r="K53" s="13"/>
-      <c r="L53" s="13">
-        <v>0</v>
-      </c>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13">
-        <v>0</v>
-      </c>
-      <c r="O53" s="13"/>
-      <c r="P53" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="13"/>
-      <c r="R53" s="13" t="s">
+      <c r="B53" s="9">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9">
+        <v>0</v>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9">
+        <v>0</v>
+      </c>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S53" s="13"/>
+      <c r="S53" s="9"/>
     </row>
     <row r="54" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13" t="s">
+      <c r="C54" s="9"/>
+      <c r="D54" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13" t="s">
+      <c r="E54" s="9"/>
+      <c r="F54" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13" t="s">
+      <c r="G54" s="9"/>
+      <c r="H54" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13" t="s">
+      <c r="I54" s="9"/>
+      <c r="J54" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13" t="s">
+      <c r="K54" s="9"/>
+      <c r="L54" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13" t="s">
+      <c r="M54" s="9"/>
+      <c r="N54" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13" t="s">
+      <c r="O54" s="9"/>
+      <c r="P54" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q54" s="13"/>
-      <c r="R54" s="13" t="s">
+      <c r="Q54" s="9"/>
+      <c r="R54" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="S54" s="13"/>
+      <c r="S54" s="9"/>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
@@ -1346,83 +1346,83 @@
       <c r="A57" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="12">
-        <v>1</v>
-      </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12">
-        <v>0</v>
-      </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12">
-        <v>1</v>
-      </c>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12">
-        <v>0</v>
-      </c>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12">
-        <v>0</v>
-      </c>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12">
-        <v>0</v>
-      </c>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12" t="s">
+      <c r="B57" s="10">
+        <v>1</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10">
+        <v>0</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10">
+        <v>1</v>
+      </c>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10">
+        <v>0</v>
+      </c>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10">
+        <v>0</v>
+      </c>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10">
+        <v>0</v>
+      </c>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10">
+        <v>0</v>
+      </c>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S57" s="12"/>
+      <c r="S57" s="10"/>
     </row>
     <row r="58" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="13">
-        <v>0</v>
-      </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13">
-        <v>0</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13">
-        <v>1</v>
-      </c>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13">
-        <v>1</v>
-      </c>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13">
-        <v>1</v>
-      </c>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13">
-        <v>1</v>
-      </c>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13">
-        <v>0</v>
-      </c>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="13"/>
-      <c r="R58" s="13" t="s">
+      <c r="B58" s="9">
+        <v>0</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9">
+        <v>1</v>
+      </c>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9">
+        <v>1</v>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9">
+        <v>1</v>
+      </c>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9">
+        <v>1</v>
+      </c>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9">
+        <v>0</v>
+      </c>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="S58" s="13"/>
+      <c r="S58" s="9"/>
       <c r="T58" s="6" t="s">
         <v>17</v>
       </c>
@@ -1471,125 +1471,189 @@
       <c r="A76" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="9"/>
-      <c r="M76" s="9"/>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
-      <c r="P76" s="9"/>
-      <c r="Q76" s="9"/>
-      <c r="R76" s="9" t="s">
+      <c r="B76" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="12"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S76" s="10"/>
+      <c r="S76" s="13"/>
     </row>
     <row r="77" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B77" s="13">
-        <v>1</v>
-      </c>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13">
-        <v>0</v>
-      </c>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13">
-        <v>1</v>
-      </c>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13">
-        <v>0</v>
-      </c>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13">
-        <v>0</v>
-      </c>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13">
-        <v>0</v>
-      </c>
-      <c r="M77" s="13"/>
-      <c r="N77" s="13">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13"/>
-      <c r="P77" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="13"/>
-      <c r="R77" s="13" t="s">
+      <c r="B77" s="9">
+        <v>1</v>
+      </c>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9">
+        <v>0</v>
+      </c>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9">
+        <v>1</v>
+      </c>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9">
+        <v>0</v>
+      </c>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9">
+        <v>0</v>
+      </c>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S77" s="13"/>
+      <c r="S77" s="9"/>
     </row>
     <row r="78" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B78" s="13">
-        <v>0</v>
-      </c>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13">
-        <v>0</v>
-      </c>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13">
-        <v>1</v>
-      </c>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13">
-        <v>1</v>
-      </c>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13">
-        <v>1</v>
-      </c>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13">
-        <v>1</v>
-      </c>
-      <c r="M78" s="13"/>
-      <c r="N78" s="13">
-        <v>0</v>
-      </c>
-      <c r="O78" s="13"/>
-      <c r="P78" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="13"/>
-      <c r="R78" s="13" t="s">
+      <c r="B78" s="9">
+        <v>0</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9">
+        <v>0</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9">
+        <v>1</v>
+      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9">
+        <v>1</v>
+      </c>
+      <c r="M78" s="9"/>
+      <c r="N78" s="9">
+        <v>0</v>
+      </c>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="S78" s="13"/>
+      <c r="S78" s="9"/>
       <c r="T78" s="6" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="R78:S78"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="B30:Q30"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="P55:Q55"/>
     <mergeCell ref="N77:O77"/>
     <mergeCell ref="P77:Q77"/>
     <mergeCell ref="R77:S77"/>
@@ -1614,79 +1678,15 @@
     <mergeCell ref="N58:O58"/>
     <mergeCell ref="P58:Q58"/>
     <mergeCell ref="R58:S58"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="B30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="N78:O78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="R78:S78"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/참고사항/TimingChart.xlsx
+++ b/참고사항/TimingChart.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <workbookPr filterPrivacy="1" codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="132">
   <si>
     <t>실제값(예시)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,438 @@
   </si>
   <si>
     <t>Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 (busy/done/nack_err 등)</t>
+  </si>
+  <si>
+    <t>현재 상태</t>
+  </si>
+  <si>
+    <t>입력조건</t>
+  </si>
+  <si>
+    <t>다음상태</t>
+  </si>
+  <si>
+    <t>IDLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd ==  2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>READ_DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start == 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitTxRx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDA_SETUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_HIGH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHIFT_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(자동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK_CHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(자동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tLow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tsu(Data)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == thigh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart == 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+  </si>
+  <si>
+    <t>BitDone == 0</t>
+  </si>
+  <si>
+    <t>cmd ==  0 or 1, ByteDone == 1, ACK == 1</t>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+  </si>
+  <si>
+    <t>Start == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, cmd == 0, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, ByteDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REP_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REP_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, cmd == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, I2cStart = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 0, ByteDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, nack_err = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 0 done =1, I2cStop = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 0, ByteDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn, BitDone=1, SdaLatch = SdaIn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount &gt; 0, BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount == 0, BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2cStop == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2cStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tHD:STA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 1, Sda = 0, BitDone = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tHD:STA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 1, Sda = 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tSU:STO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 0, Sda = 1, BitDone = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tSU:STO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 0, Sda = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tLow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tsu(Data)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; thigh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount = 7, BitStart=1, DriveEn=rw==Write?1:0, reg = WriteData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart = 1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart=1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1, DriveEn = rw==Write ? 0:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK = SdaLatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteDone = 1, ReadData = reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = 0xA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = 0xA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = Addr[14:8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = addr[7:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = WData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = addr[7:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, WriteData = 0xA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>READ_DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, Rdata = ReadData</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -108,7 +540,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,8 +555,24 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,8 +591,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F497D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -259,11 +713,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -275,6 +744,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -297,7 +781,554 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="39">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -354,14 +1385,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>952500</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>491479</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>111801</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>102563</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -392,13 +1423,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>952501</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>624178</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>68687</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -465,6 +1496,45 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="V7:Y26" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
+  <autoFilter ref="V7:Y26"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="2" name="입력조건" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="3" name="다음상태" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="4" name="출력 (busy/done/nack_err 등)" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표1_3" displayName="표1_3" ref="V29:Y43" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+  <autoFilter ref="V29:Y43"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="2" name="입력조건" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="3" name="다음상태" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="4" name="출력 (busy/done/nack_err 등)" totalsRowFunction="count" dataDxfId="14" totalsRowDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="표1_34" displayName="표1_34" ref="V46:Y55" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="V46:Y55"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="2" name="입력조건" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" name="다음상태" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" name="출력 (busy/done/nack_err 등)" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -754,14 +1824,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:U78"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A2:Y86"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="1"/>
+    <col min="2" max="21" width="9" style="1"/>
+    <col min="22" max="22" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="33.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="4"/>
       <c r="E2" s="4"/>
       <c r="G2" s="4"/>
@@ -772,7 +1848,7 @@
       <c r="Q2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
       <c r="D3" s="2"/>
@@ -794,7 +1870,7 @@
       <c r="T3" s="2"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
@@ -806,11 +1882,184 @@
       <c r="R4" s="4"/>
       <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.3">
       <c r="I5" s="4"/>
       <c r="P5" s="4"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V17" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -832,8 +2081,20 @@
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y19" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -855,8 +2116,20 @@
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y20" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -878,8 +2151,20 @@
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y21" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -901,8 +2186,20 @@
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y22" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -924,772 +2221,1364 @@
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
-    </row>
-    <row r="28" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
+      <c r="V23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W23" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y23" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="W24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y24" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="W25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y26" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y29" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="W30" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="X30" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y30" s="13"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="W31" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="X31" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y31" s="13"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V32" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="W32" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="X32" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y32" s="13"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y33" s="13"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V34" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="W34" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="X34" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y34" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V35" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="W35" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="X35" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y35" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V36" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="W36" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="X36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y36" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="3"/>
+      <c r="V37" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="W37" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="X37" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y37" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12" t="s">
+      <c r="B38" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="S30" s="13"/>
-    </row>
-    <row r="31" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+      <c r="S38" s="18"/>
+      <c r="V38" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="W38" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y38" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B39" s="14">
         <v>1</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9">
-        <v>0</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9">
-        <v>0</v>
-      </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9">
-        <v>0</v>
-      </c>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9" t="s">
+      <c r="G39" s="14"/>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14">
+        <v>0</v>
+      </c>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14">
+        <v>0</v>
+      </c>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14">
+        <v>0</v>
+      </c>
+      <c r="O39" s="14"/>
+      <c r="P39" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="14"/>
+      <c r="R39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="S31" s="9"/>
-    </row>
-    <row r="32" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+      <c r="S39" s="14"/>
+      <c r="V39" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="W39" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="X39" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y39" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B40" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9" t="s">
+      <c r="E40" s="14"/>
+      <c r="F40" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9" t="s">
+      <c r="G40" s="14"/>
+      <c r="H40" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9" t="s">
+      <c r="I40" s="14"/>
+      <c r="J40" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9" t="s">
+      <c r="K40" s="14"/>
+      <c r="L40" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9" t="s">
+      <c r="M40" s="14"/>
+      <c r="N40" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9" t="s">
+      <c r="O40" s="14"/>
+      <c r="P40" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9" t="s">
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="S32" s="9"/>
-    </row>
-    <row r="33" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="S40" s="14"/>
+      <c r="V40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y40" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9" t="s">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
+      <c r="E41" s="14"/>
+      <c r="F41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9" t="s">
+      <c r="G41" s="14"/>
+      <c r="H41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9" t="s">
+      <c r="I41" s="14"/>
+      <c r="J41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9" t="s">
+      <c r="K41" s="14"/>
+      <c r="L41" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9" t="s">
+      <c r="M41" s="14"/>
+      <c r="N41" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9" t="s">
+      <c r="O41" s="14"/>
+      <c r="P41" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9" t="s">
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="S33" s="9"/>
-    </row>
-    <row r="34" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
+      <c r="S41" s="14"/>
+      <c r="V41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="W41" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y41" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="9">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9">
+      <c r="B42" s="14">
+        <v>0</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14">
         <v>1</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9">
+      <c r="G42" s="14"/>
+      <c r="H42" s="14">
         <v>1</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9">
+      <c r="I42" s="14"/>
+      <c r="J42" s="14">
         <v>1</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9">
+      <c r="K42" s="14"/>
+      <c r="L42" s="14">
         <v>1</v>
       </c>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9">
-        <v>0</v>
-      </c>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9" t="s">
+      <c r="M42" s="14"/>
+      <c r="N42" s="14">
+        <v>0</v>
+      </c>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="S34" s="9"/>
-      <c r="T34" s="6" t="s">
+      <c r="S42" s="14"/>
+      <c r="T42" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
+      <c r="V42" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="X42" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y42" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V43" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W43" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y43" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V44" s="11"/>
+      <c r="W44" s="11"/>
+      <c r="X44" s="11"/>
+      <c r="Y44" s="11"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V45" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V46" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W46" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="X46" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y46" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V47" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="W47" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y47" s="9"/>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V48" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y48" s="9"/>
+    </row>
+    <row r="49" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="V49" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y49" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y50" s="9"/>
+    </row>
+    <row r="51" spans="1:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="X51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y51" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="V52" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="X52" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y52" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V53" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="W53" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="X53" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y53" s="9"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V54" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="W54" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X54" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y54" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V55" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W55" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="X55" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y55" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V56" s="12"/>
+      <c r="W56" s="12"/>
+      <c r="X56" s="12"/>
+      <c r="Y56" s="12"/>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V57" s="12"/>
+      <c r="W57" s="12"/>
+      <c r="X57" s="12"/>
+      <c r="Y57" s="12"/>
+    </row>
+    <row r="58" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V58" s="12"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="12"/>
+      <c r="Y58" s="12"/>
+    </row>
+    <row r="59" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="12"/>
-      <c r="R52" s="12" t="s">
+      <c r="B60" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="S52" s="13"/>
-    </row>
-    <row r="53" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
+      <c r="S60" s="18"/>
+    </row>
+    <row r="61" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B61" s="14">
         <v>1</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9">
-        <v>0</v>
-      </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9">
+      <c r="C61" s="14"/>
+      <c r="D61" s="14">
+        <v>0</v>
+      </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14">
         <v>1</v>
       </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9">
-        <v>0</v>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9">
-        <v>0</v>
-      </c>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9">
-        <v>0</v>
-      </c>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9" t="s">
+      <c r="G61" s="14"/>
+      <c r="H61" s="14">
+        <v>0</v>
+      </c>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14">
+        <v>0</v>
+      </c>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14">
+        <v>0</v>
+      </c>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14">
+        <v>0</v>
+      </c>
+      <c r="O61" s="14"/>
+      <c r="P61" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="S53" s="9"/>
-    </row>
-    <row r="54" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="7" t="s">
+      <c r="S61" s="14"/>
+    </row>
+    <row r="62" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B62" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9" t="s">
+      <c r="C62" s="14"/>
+      <c r="D62" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9" t="s">
+      <c r="E62" s="14"/>
+      <c r="F62" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9" t="s">
+      <c r="G62" s="14"/>
+      <c r="H62" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9" t="s">
+      <c r="I62" s="14"/>
+      <c r="J62" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9" t="s">
+      <c r="K62" s="14"/>
+      <c r="L62" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9" t="s">
+      <c r="M62" s="14"/>
+      <c r="N62" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9" t="s">
+      <c r="O62" s="14"/>
+      <c r="P62" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Q54" s="9"/>
-      <c r="R54" s="9" t="s">
+      <c r="Q62" s="14"/>
+      <c r="R62" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="S54" s="9"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="S62" s="14"/>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14" t="s">
+      <c r="C63" s="19"/>
+      <c r="D63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14" t="s">
+      <c r="E63" s="19"/>
+      <c r="F63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14" t="s">
+      <c r="G63" s="19"/>
+      <c r="H63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14" t="s">
+      <c r="I63" s="19"/>
+      <c r="J63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14" t="s">
+      <c r="K63" s="19"/>
+      <c r="L63" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14" t="s">
+      <c r="M63" s="19"/>
+      <c r="N63" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="O55" s="14"/>
-      <c r="P55" s="14" t="s">
+      <c r="O63" s="19"/>
+      <c r="P63" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q55" s="14"/>
-      <c r="R55" s="14" t="s">
+      <c r="Q63" s="19"/>
+      <c r="R63" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="S55" s="14"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+      <c r="S63" s="19"/>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B64" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="11"/>
-      <c r="R56" s="11"/>
-      <c r="S56" s="11"/>
-    </row>
-    <row r="57" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16"/>
+      <c r="P64" s="16"/>
+      <c r="Q64" s="16"/>
+      <c r="R64" s="16"/>
+      <c r="S64" s="16"/>
+    </row>
+    <row r="65" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B65" s="15">
         <v>1</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10">
-        <v>0</v>
-      </c>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10">
+      <c r="C65" s="15"/>
+      <c r="D65" s="15">
+        <v>0</v>
+      </c>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15">
         <v>1</v>
       </c>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10">
-        <v>0</v>
-      </c>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10">
-        <v>0</v>
-      </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10">
-        <v>0</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10">
-        <v>0</v>
-      </c>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10">
+      <c r="G65" s="15"/>
+      <c r="H65" s="15">
+        <v>0</v>
+      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15">
+        <v>0</v>
+      </c>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15">
+        <v>0</v>
+      </c>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15">
+        <v>0</v>
+      </c>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15">
         <v>1</v>
       </c>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10" t="s">
+      <c r="Q65" s="15"/>
+      <c r="R65" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="S57" s="10"/>
-    </row>
-    <row r="58" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+      <c r="S65" s="15"/>
+    </row>
+    <row r="66" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="9">
-        <v>0</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9">
-        <v>0</v>
-      </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9">
+      <c r="B66" s="14">
+        <v>0</v>
+      </c>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14">
+        <v>0</v>
+      </c>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14">
         <v>1</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9">
+      <c r="G66" s="14"/>
+      <c r="H66" s="14">
         <v>1</v>
       </c>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9">
+      <c r="I66" s="14"/>
+      <c r="J66" s="14">
         <v>1</v>
       </c>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9">
+      <c r="K66" s="14"/>
+      <c r="L66" s="14">
         <v>1</v>
       </c>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9">
-        <v>0</v>
-      </c>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="9" t="s">
+      <c r="M66" s="14"/>
+      <c r="N66" s="14">
+        <v>0</v>
+      </c>
+      <c r="O66" s="14"/>
+      <c r="P66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="14"/>
+      <c r="R66" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="S58" s="9"/>
-      <c r="T58" s="6" t="s">
+      <c r="S66" s="14"/>
+      <c r="T66" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
+    <row r="82" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B83" s="2">
         <v>1</v>
       </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="2">
+      <c r="C83" s="3"/>
+      <c r="D83" s="2">
         <v>2</v>
       </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="2">
+      <c r="E83" s="3"/>
+      <c r="F83" s="2">
         <v>3</v>
       </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="2">
+      <c r="G83" s="3"/>
+      <c r="H83" s="2">
         <v>4</v>
       </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="2">
+      <c r="I83" s="3"/>
+      <c r="J83" s="2">
         <v>5</v>
       </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="2">
+      <c r="K83" s="3"/>
+      <c r="L83" s="2">
         <v>6</v>
       </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="2">
+      <c r="M83" s="3"/>
+      <c r="N83" s="2">
         <v>7</v>
       </c>
-      <c r="O75" s="3"/>
-      <c r="P75" s="2">
+      <c r="O83" s="3"/>
+      <c r="P83" s="2">
         <v>8</v>
       </c>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="8" t="s">
+      <c r="Q83" s="3"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="12"/>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="12" t="s">
+      <c r="B84" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="17"/>
+      <c r="N84" s="17"/>
+      <c r="O84" s="17"/>
+      <c r="P84" s="17"/>
+      <c r="Q84" s="17"/>
+      <c r="R84" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="S76" s="13"/>
-    </row>
-    <row r="77" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="7" t="s">
+      <c r="S84" s="18"/>
+    </row>
+    <row r="85" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B85" s="14">
         <v>1</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9">
-        <v>0</v>
-      </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9">
+      <c r="C85" s="14"/>
+      <c r="D85" s="14">
+        <v>0</v>
+      </c>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14">
         <v>1</v>
       </c>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9">
-        <v>0</v>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9">
-        <v>0</v>
-      </c>
-      <c r="K77" s="9"/>
-      <c r="L77" s="9">
-        <v>0</v>
-      </c>
-      <c r="M77" s="9"/>
-      <c r="N77" s="9">
-        <v>0</v>
-      </c>
-      <c r="O77" s="9"/>
-      <c r="P77" s="9">
+      <c r="G85" s="14"/>
+      <c r="H85" s="14">
+        <v>0</v>
+      </c>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14">
+        <v>0</v>
+      </c>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14">
+        <v>0</v>
+      </c>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14">
+        <v>0</v>
+      </c>
+      <c r="O85" s="14"/>
+      <c r="P85" s="14">
         <v>1</v>
       </c>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9" t="s">
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="S77" s="9"/>
-    </row>
-    <row r="78" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="7" t="s">
+      <c r="S85" s="14"/>
+    </row>
+    <row r="86" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B78" s="9">
-        <v>0</v>
-      </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9">
-        <v>0</v>
-      </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9">
+      <c r="B86" s="14">
+        <v>0</v>
+      </c>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14">
+        <v>0</v>
+      </c>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14">
         <v>1</v>
       </c>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9">
+      <c r="G86" s="14"/>
+      <c r="H86" s="14">
         <v>1</v>
       </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9">
+      <c r="I86" s="14"/>
+      <c r="J86" s="14">
         <v>1</v>
       </c>
-      <c r="K78" s="9"/>
-      <c r="L78" s="9">
+      <c r="K86" s="14"/>
+      <c r="L86" s="14">
         <v>1</v>
       </c>
-      <c r="M78" s="9"/>
-      <c r="N78" s="9">
-        <v>0</v>
-      </c>
-      <c r="O78" s="9"/>
-      <c r="P78" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="9"/>
-      <c r="R78" s="9" t="s">
+      <c r="M86" s="14"/>
+      <c r="N86" s="14">
+        <v>0</v>
+      </c>
+      <c r="O86" s="14"/>
+      <c r="P86" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="14"/>
+      <c r="R86" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="S78" s="9"/>
-      <c r="T78" s="6" t="s">
+      <c r="S86" s="14"/>
+      <c r="T86" s="6" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="B30:Q30"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="N77:O77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="R57:S57"/>
-    <mergeCell ref="B56:S56"/>
-    <mergeCell ref="B76:Q76"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="R58:S58"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="R78:S78"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="B38:Q38"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="B64:S64"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="R84:S84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="R86:S86"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="3">
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>